--- a/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1394,17 +1386,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1484,17 +1468,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1574,17 +1550,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1664,17 +1632,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1754,17 +1714,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -1844,17 +1796,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -1934,17 +1878,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -2024,17 +1960,9 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="inlineStr">
@@ -2114,17 +2042,9 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2204,17 +2124,9 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
@@ -2294,17 +2206,9 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2384,17 +2288,9 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2474,17 +2370,9 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2564,17 +2452,9 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="inlineStr">
@@ -2654,17 +2534,9 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="inlineStr">
@@ -2743,16 +2615,8 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2798,16 +2662,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2853,16 +2709,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2908,16 +2756,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2963,16 +2803,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3018,16 +2850,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3073,16 +2897,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3128,16 +2944,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3183,16 +2991,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3238,16 +3038,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3293,16 +3085,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3348,16 +3132,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3403,16 +3179,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1550,11 +1610,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1632,11 +1712,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1714,11 +1814,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1796,11 +1916,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1878,11 +2018,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1960,11 +2120,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2042,11 +2222,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2124,11 +2324,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2206,11 +2426,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2288,11 +2528,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2370,11 +2630,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2452,11 +2732,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2534,11 +2834,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2615,8 +2935,31 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2662,8 +3005,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2709,8 +3075,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2756,8 +3145,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2803,8 +3215,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2850,8 +3285,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2897,8 +3355,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2944,8 +3425,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2991,8 +3495,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3038,8 +3565,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3085,8 +3635,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3132,8 +3705,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3179,8 +3775,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV35"/>
+  <dimension ref="A1:AV64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3844,6 +3844,2036 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>19</v>
+      </c>
+      <c r="K36" t="n">
+        <v>60</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>20</v>
+      </c>
+      <c r="P36" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>19</v>
+      </c>
+      <c r="K37" t="n">
+        <v>54</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>60</v>
+      </c>
+      <c r="P37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" t="n">
+        <v>60</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>70</v>
+      </c>
+      <c r="P38" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" t="n">
+        <v>60</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>80</v>
+      </c>
+      <c r="P39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>19</v>
+      </c>
+      <c r="K40" t="n">
+        <v>60</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>100</v>
+      </c>
+      <c r="P40" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>19</v>
+      </c>
+      <c r="K41" t="n">
+        <v>60</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>20</v>
+      </c>
+      <c r="P41" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>19</v>
+      </c>
+      <c r="K42" t="n">
+        <v>48</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>60</v>
+      </c>
+      <c r="P42" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>19</v>
+      </c>
+      <c r="K43" t="n">
+        <v>59</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>70</v>
+      </c>
+      <c r="P43" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>19</v>
+      </c>
+      <c r="K44" t="n">
+        <v>60</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>80</v>
+      </c>
+      <c r="P44" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>19</v>
+      </c>
+      <c r="K45" t="n">
+        <v>60</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>100</v>
+      </c>
+      <c r="P45" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>28</v>
+      </c>
+      <c r="K46" t="n">
+        <v>60</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>20</v>
+      </c>
+      <c r="P46" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>19</v>
+      </c>
+      <c r="K47" t="n">
+        <v>43</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>60</v>
+      </c>
+      <c r="P47" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>19</v>
+      </c>
+      <c r="K48" t="n">
+        <v>54</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>70</v>
+      </c>
+      <c r="P48" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>19</v>
+      </c>
+      <c r="K49" t="n">
+        <v>60</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>80</v>
+      </c>
+      <c r="P49" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>19</v>
+      </c>
+      <c r="K50" t="n">
+        <v>60</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>100</v>
+      </c>
+      <c r="P50" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>19</v>
+      </c>
+      <c r="K51" t="n">
+        <v>38</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>60</v>
+      </c>
+      <c r="P51" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>19</v>
+      </c>
+      <c r="K52" t="n">
+        <v>49</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>70</v>
+      </c>
+      <c r="P52" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>19</v>
+      </c>
+      <c r="K53" t="n">
+        <v>59</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>80</v>
+      </c>
+      <c r="P53" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>19</v>
+      </c>
+      <c r="K54" t="n">
+        <v>60</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>100</v>
+      </c>
+      <c r="P54" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>19</v>
+      </c>
+      <c r="K55" t="n">
+        <v>39</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>70</v>
+      </c>
+      <c r="P55" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>19</v>
+      </c>
+      <c r="K56" t="n">
+        <v>49</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>80</v>
+      </c>
+      <c r="P56" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>19</v>
+      </c>
+      <c r="K57" t="n">
+        <v>60</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>100</v>
+      </c>
+      <c r="P57" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>19</v>
+      </c>
+      <c r="K58" t="n">
+        <v>54</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>70</v>
+      </c>
+      <c r="P58" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>19</v>
+      </c>
+      <c r="K59" t="n">
+        <v>54</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>80</v>
+      </c>
+      <c r="P59" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>19</v>
+      </c>
+      <c r="K60" t="n">
+        <v>54</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>100</v>
+      </c>
+      <c r="P60" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>19</v>
+      </c>
+      <c r="K61" t="n">
+        <v>33</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>60</v>
+      </c>
+      <c r="P61" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>19</v>
+      </c>
+      <c r="K62" t="n">
+        <v>37</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>70</v>
+      </c>
+      <c r="P62" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>19</v>
+      </c>
+      <c r="K63" t="n">
+        <v>60</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>80</v>
+      </c>
+      <c r="P63" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2061002</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>19</v>
+      </c>
+      <c r="K64" t="n">
+        <v>60</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>100</v>
+      </c>
+      <c r="P64" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>

--- a/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00026_2061_e암보험_비갱신형_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>19</v>
       </c>
@@ -1441,7 +1445,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>19</v>
       </c>
@@ -1543,7 +1551,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>19</v>
       </c>
@@ -1645,7 +1657,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>19</v>
       </c>
@@ -1747,7 +1763,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="6" t="n">
         <v>19</v>
       </c>
@@ -1849,7 +1869,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="n">
         <v>19</v>
       </c>
@@ -1951,7 +1975,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="n">
         <v>19</v>
       </c>
@@ -2053,7 +2081,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n">
         <v>19</v>
       </c>
@@ -2155,7 +2187,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="n">
         <v>19</v>
       </c>
@@ -2257,7 +2293,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="n">
         <v>19</v>
       </c>
@@ -2359,7 +2399,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="n">
         <v>28</v>
       </c>
@@ -2461,7 +2505,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="n">
         <v>19</v>
       </c>
@@ -2563,7 +2611,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="n">
         <v>19</v>
       </c>
@@ -2665,7 +2717,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="n">
         <v>19</v>
       </c>
@@ -2767,7 +2823,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J21" s="6" t="n">
         <v>19</v>
       </c>
@@ -2869,7 +2929,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="n">
         <v>19</v>
       </c>
@@ -2970,6 +3034,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J23" t="n">
         <v>19</v>
       </c>
@@ -3040,6 +3109,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J24" t="n">
         <v>19</v>
       </c>
@@ -3110,6 +3184,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J25" t="n">
         <v>19</v>
       </c>
@@ -3180,6 +3259,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J26" t="n">
         <v>19</v>
       </c>
@@ -3250,6 +3334,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J27" t="n">
         <v>19</v>
       </c>
@@ -3320,6 +3409,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J28" t="n">
         <v>19</v>
       </c>
@@ -3390,6 +3484,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J29" t="n">
         <v>19</v>
       </c>
@@ -3460,6 +3559,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J30" t="n">
         <v>19</v>
       </c>
@@ -3530,6 +3634,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J31" t="n">
         <v>19</v>
       </c>
@@ -3600,6 +3709,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J32" t="n">
         <v>19</v>
       </c>
@@ -3670,6 +3784,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J33" t="n">
         <v>19</v>
       </c>
@@ -3740,6 +3859,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J34" t="n">
         <v>19</v>
       </c>
@@ -3810,6 +3934,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J35" t="n">
         <v>19</v>
       </c>
@@ -3880,6 +4009,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J36" t="n">
         <v>19</v>
       </c>
@@ -3950,6 +4084,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J37" t="n">
         <v>19</v>
       </c>
@@ -4020,6 +4159,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J38" t="n">
         <v>19</v>
       </c>
@@ -4090,6 +4234,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J39" t="n">
         <v>19</v>
       </c>
@@ -4160,6 +4309,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J40" t="n">
         <v>19</v>
       </c>
@@ -4230,6 +4384,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J41" t="n">
         <v>19</v>
       </c>
@@ -4300,6 +4459,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J42" t="n">
         <v>19</v>
       </c>
@@ -4370,6 +4534,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J43" t="n">
         <v>19</v>
       </c>
@@ -4440,6 +4609,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J44" t="n">
         <v>19</v>
       </c>
@@ -4510,6 +4684,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J45" t="n">
         <v>19</v>
       </c>
@@ -4580,6 +4759,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J46" t="n">
         <v>28</v>
       </c>
@@ -4650,6 +4834,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J47" t="n">
         <v>19</v>
       </c>
@@ -4720,6 +4909,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J48" t="n">
         <v>19</v>
       </c>
@@ -4790,6 +4984,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J49" t="n">
         <v>19</v>
       </c>
@@ -4860,6 +5059,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J50" t="n">
         <v>19</v>
       </c>
@@ -4930,6 +5134,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J51" t="n">
         <v>19</v>
       </c>
@@ -5000,6 +5209,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J52" t="n">
         <v>19</v>
       </c>
@@ -5070,6 +5284,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J53" t="n">
         <v>19</v>
       </c>
@@ -5140,6 +5359,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J54" t="n">
         <v>19</v>
       </c>
@@ -5210,6 +5434,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J55" t="n">
         <v>19</v>
       </c>
@@ -5280,6 +5509,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J56" t="n">
         <v>19</v>
       </c>
@@ -5350,6 +5584,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J57" t="n">
         <v>19</v>
       </c>
@@ -5420,6 +5659,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J58" t="n">
         <v>19</v>
       </c>
@@ -5490,6 +5734,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J59" t="n">
         <v>19</v>
       </c>
@@ -5560,6 +5809,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J60" t="n">
         <v>19</v>
       </c>
@@ -5630,6 +5884,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J61" t="n">
         <v>19</v>
       </c>
@@ -5700,6 +5959,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J62" t="n">
         <v>19</v>
       </c>
@@ -5770,6 +6034,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J63" t="n">
         <v>19</v>
       </c>
@@ -5838,6 +6107,11 @@
       <c r="H64" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="n">
